--- a/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-koerpergewicht.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-koerpergewicht</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-koerpergewicht</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -116,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-vitalparameter</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-vitalparameter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -823,7 +823,7 @@
     <t>Observation.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-device-phg)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-device-phg)
 </t>
   </si>
   <si>
@@ -1473,7 +1473,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="urn:iso:std:iso:11073:10101"/&gt;
-  &lt;code value="188800"/&gt;
+  &lt;code value="188736"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -1582,7 +1582,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -2312,7 +2312,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-device-phd)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-device-phd)
 </t>
   </si>
   <si>
